--- a/rozpis_sluzeb_byt.xlsx
+++ b/rozpis_sluzeb_byt.xlsx
@@ -105,7 +105,7 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="002E75B6"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -525,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -566,9 +566,6 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -576,9 +573,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1046,8 +1040,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -1056,7 +1050,6 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1128,11 +1121,6 @@
 (Společné + Koup/WC)</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Splněno / Kontrola</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -1168,43 +1156,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Týden 2</t>
         </is>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="15">
         <f>$B$4 + (1*7)</f>
         <v/>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <f>B8 + 6</f>
         <v/>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -1240,43 +1226,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Týden 4</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="15">
         <f>$B$4 + (3*7)</f>
         <v/>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="15">
         <f>B10 + 6</f>
         <v/>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -1312,43 +1296,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Týden 6</t>
         </is>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="15">
         <f>$B$4 + (5*7)</f>
         <v/>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="15">
         <f>B12 + 6</f>
         <v/>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -1384,43 +1366,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Týden 8</t>
         </is>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="15">
         <f>$B$4 + (7*7)</f>
         <v/>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="15">
         <f>B14 + 6</f>
         <v/>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -1456,43 +1436,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Týden 10</t>
         </is>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="15">
         <f>$B$4 + (9*7)</f>
         <v/>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="15">
         <f>B16 + 6</f>
         <v/>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -1528,43 +1506,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Týden 12</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="15">
         <f>$B$4 + (11*7)</f>
         <v/>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="15">
         <f>B18 + 6</f>
         <v/>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -1600,43 +1576,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Týden 14</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="15">
         <f>$B$4 + (13*7)</f>
         <v/>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="15">
         <f>B20 + 6</f>
         <v/>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -1672,43 +1646,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Týden 16</t>
         </is>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="15">
         <f>$B$4 + (15*7)</f>
         <v/>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="15">
         <f>B22 + 6</f>
         <v/>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -1744,43 +1716,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Týden 18</t>
         </is>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="15">
         <f>$B$4 + (17*7)</f>
         <v/>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="15">
         <f>B24 + 6</f>
         <v/>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -1816,43 +1786,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Týden 20</t>
         </is>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="15">
         <f>$B$4 + (19*7)</f>
         <v/>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="15">
         <f>B26 + 6</f>
         <v/>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H26" s="18" t="inlineStr"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -1888,43 +1856,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Týden 22</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="15">
         <f>$B$4 + (21*7)</f>
         <v/>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="15">
         <f>B28 + 6</f>
         <v/>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -1960,43 +1926,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Týden 24</t>
         </is>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="15">
         <f>$B$4 + (23*7)</f>
         <v/>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="15">
         <f>B30 + 6</f>
         <v/>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H30" s="18" t="inlineStr"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -2032,43 +1996,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Týden 26</t>
         </is>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="15">
         <f>$B$4 + (25*7)</f>
         <v/>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="15">
         <f>B32 + 6</f>
         <v/>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H32" s="18" t="inlineStr"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
@@ -2104,43 +2066,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Týden 28</t>
         </is>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="15">
         <f>$B$4 + (27*7)</f>
         <v/>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="15">
         <f>B34 + 6</f>
         <v/>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H34" s="18" t="inlineStr"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
@@ -2176,43 +2136,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr"/>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Týden 30</t>
         </is>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="15">
         <f>$B$4 + (29*7)</f>
         <v/>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="15">
         <f>B36 + 6</f>
         <v/>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H36" s="18" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
@@ -2248,43 +2206,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H37" s="14" t="inlineStr"/>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Týden 32</t>
         </is>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="15">
         <f>$B$4 + (31*7)</f>
         <v/>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="15">
         <f>B38 + 6</f>
         <v/>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H38" s="18" t="inlineStr"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -2320,43 +2276,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Týden 34</t>
         </is>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="15">
         <f>$B$4 + (33*7)</f>
         <v/>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="15">
         <f>B40 + 6</f>
         <v/>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H40" s="18" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
@@ -2392,43 +2346,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr"/>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>Týden 36</t>
         </is>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="15">
         <f>$B$4 + (35*7)</f>
         <v/>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="15">
         <f>B42 + 6</f>
         <v/>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G42" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H42" s="18" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
@@ -2464,43 +2416,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>Týden 38</t>
         </is>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="15">
         <f>$B$4 + (37*7)</f>
         <v/>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="15">
         <f>B44 + 6</f>
         <v/>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G44" s="17" t="inlineStr">
+      <c r="G44" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H44" s="18" t="inlineStr"/>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
@@ -2536,43 +2486,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>Týden 40</t>
         </is>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="15">
         <f>$B$4 + (39*7)</f>
         <v/>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="15">
         <f>B46 + 6</f>
         <v/>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="G46" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H46" s="18" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
@@ -2608,43 +2556,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr"/>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>Týden 42</t>
         </is>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="15">
         <f>$B$4 + (41*7)</f>
         <v/>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="15">
         <f>B48 + 6</f>
         <v/>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F48" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G48" s="17" t="inlineStr">
+      <c r="G48" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H48" s="18" t="inlineStr"/>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
@@ -2680,43 +2626,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Týden 44</t>
         </is>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="15">
         <f>$B$4 + (43*7)</f>
         <v/>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="15">
         <f>B50 + 6</f>
         <v/>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F50" s="17" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G50" s="17" t="inlineStr">
+      <c r="G50" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H50" s="18" t="inlineStr"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
@@ -2752,43 +2696,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H51" s="14" t="inlineStr"/>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Týden 46</t>
         </is>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="15">
         <f>$B$4 + (45*7)</f>
         <v/>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="15">
         <f>B52 + 6</f>
         <v/>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="F52" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G52" s="17" t="inlineStr">
+      <c r="G52" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H52" s="18" t="inlineStr"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
@@ -2824,43 +2766,41 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H53" s="14" t="inlineStr"/>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>Týden 48</t>
         </is>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="15">
         <f>$B$4 + (47*7)</f>
         <v/>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="15">
         <f>B54 + 6</f>
         <v/>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr">
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F54" s="17" t="inlineStr">
+      <c r="F54" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G54" s="17" t="inlineStr">
+      <c r="G54" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H54" s="18" t="inlineStr"/>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
@@ -2896,43 +2836,41 @@
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="H55" s="14" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>Týden 50</t>
         </is>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="15">
         <f>$B$4 + (49*7)</f>
         <v/>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="15">
         <f>B56 + 6</f>
         <v/>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
+      <c r="E56" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="F56" s="17" t="inlineStr">
+      <c r="F56" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
+      <c r="G56" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="H56" s="18" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
@@ -2968,49 +2906,47 @@
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="H57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>Týden 52</t>
         </is>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="15">
         <f>$B$4 + (51*7)</f>
         <v/>
       </c>
-      <c r="C58" s="16">
+      <c r="C58" s="15">
         <f>B58 + 6</f>
         <v/>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>Kuchyň  +  WC</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>Odpadky  +  Koupelna</t>
         </is>
       </c>
-      <c r="F58" s="17" t="inlineStr">
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>Předsíň  +  WC</t>
         </is>
       </c>
-      <c r="G58" s="17" t="inlineStr">
+      <c r="G58" s="16" t="inlineStr">
         <is>
           <t>Schody  +  Koupelna</t>
         </is>
       </c>
-      <c r="H58" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3023,7 +2959,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -3053,17 +2989,17 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>TERMÍN</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>🧹 SPOLEČNÉ PROSTORY (ROTACE VŠECH 4 POKOJŮ)</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>🚿 KOUPELNY A ZÁCHODY (ROTACE DVOJIC)</t>
         </is>
@@ -3085,42 +3021,42 @@
           <t>Do (Ne)</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Schody</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>Kuchyň</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>Odpadky</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>Předsíň</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>Koupelna (P1-P2)</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>WC (P1-P2)</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>Koupelna (P3-P4)</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>WC (P3-P4)</t>
         </is>
@@ -3132,105 +3068,105 @@
           <t>Týden 1</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="22">
         <f>'Rozpis podle pokojů'!B7</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="22">
         <f>'Rozpis podle pokojů'!C7</f>
         <v/>
       </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I6" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J6" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Týden 2</t>
         </is>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="27">
         <f>'Rozpis podle pokojů'!B8</f>
         <v/>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="27">
         <f>'Rozpis podle pokojů'!C8</f>
         <v/>
       </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E7" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F7" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G7" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H7" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I7" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J7" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J7" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -3242,105 +3178,105 @@
           <t>Týden 3</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="22">
         <f>'Rozpis podle pokojů'!B9</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="22">
         <f>'Rozpis podle pokojů'!C9</f>
         <v/>
       </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G8" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I8" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J8" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K8" s="28" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Týden 4</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="27">
         <f>'Rozpis podle pokojů'!B10</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="27">
         <f>'Rozpis podle pokojů'!C10</f>
         <v/>
       </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E9" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F9" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G9" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H9" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I9" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J9" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K9" s="27" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -3352,105 +3288,105 @@
           <t>Týden 5</t>
         </is>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="22">
         <f>'Rozpis podle pokojů'!B11</f>
         <v/>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="22">
         <f>'Rozpis podle pokojů'!C11</f>
         <v/>
       </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E10" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H10" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I10" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J10" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K10" s="28" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Týden 6</t>
         </is>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="27">
         <f>'Rozpis podle pokojů'!B12</f>
         <v/>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="27">
         <f>'Rozpis podle pokojů'!C12</f>
         <v/>
       </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G11" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H11" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I11" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J11" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -3462,105 +3398,105 @@
           <t>Týden 7</t>
         </is>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="22">
         <f>'Rozpis podle pokojů'!B13</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="22">
         <f>'Rozpis podle pokojů'!C13</f>
         <v/>
       </c>
-      <c r="D12" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F12" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G12" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J12" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K12" s="28" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Týden 8</t>
         </is>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="27">
         <f>'Rozpis podle pokojů'!B14</f>
         <v/>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="27">
         <f>'Rozpis podle pokojů'!C14</f>
         <v/>
       </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F13" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G13" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H13" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I13" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J13" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K13" s="27" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J13" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -3572,105 +3508,105 @@
           <t>Týden 9</t>
         </is>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="22">
         <f>'Rozpis podle pokojů'!B15</f>
         <v/>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="22">
         <f>'Rozpis podle pokojů'!C15</f>
         <v/>
       </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G14" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I14" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J14" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Týden 10</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="27">
         <f>'Rozpis podle pokojů'!B16</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="27">
         <f>'Rozpis podle pokojů'!C16</f>
         <v/>
       </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E15" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F15" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G15" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H15" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J15" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K15" s="27" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K15" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -3682,105 +3618,105 @@
           <t>Týden 11</t>
         </is>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="22">
         <f>'Rozpis podle pokojů'!B17</f>
         <v/>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="22">
         <f>'Rozpis podle pokojů'!C17</f>
         <v/>
       </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G16" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K16" s="28" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Týden 12</t>
         </is>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="27">
         <f>'Rozpis podle pokojů'!B18</f>
         <v/>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="27">
         <f>'Rozpis podle pokojů'!C18</f>
         <v/>
       </c>
-      <c r="D17" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F17" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G17" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H17" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J17" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K17" s="27" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -3792,105 +3728,105 @@
           <t>Týden 13</t>
         </is>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="22">
         <f>'Rozpis podle pokojů'!B19</f>
         <v/>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="22">
         <f>'Rozpis podle pokojů'!C19</f>
         <v/>
       </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G18" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J18" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K18" s="28" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Týden 14</t>
         </is>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="27">
         <f>'Rozpis podle pokojů'!B20</f>
         <v/>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="27">
         <f>'Rozpis podle pokojů'!C20</f>
         <v/>
       </c>
-      <c r="D19" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F19" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G19" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H19" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I19" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J19" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K19" s="27" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K19" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -3902,105 +3838,105 @@
           <t>Týden 15</t>
         </is>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="22">
         <f>'Rozpis podle pokojů'!B21</f>
         <v/>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="22">
         <f>'Rozpis podle pokojů'!C21</f>
         <v/>
       </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G20" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H20" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I20" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K20" s="28" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Týden 16</t>
         </is>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="27">
         <f>'Rozpis podle pokojů'!B22</f>
         <v/>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="27">
         <f>'Rozpis podle pokojů'!C22</f>
         <v/>
       </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F21" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G21" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H21" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I21" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J21" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K21" s="27" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J21" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K21" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -4012,105 +3948,105 @@
           <t>Týden 17</t>
         </is>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="22">
         <f>'Rozpis podle pokojů'!B23</f>
         <v/>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="22">
         <f>'Rozpis podle pokojů'!C23</f>
         <v/>
       </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G22" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H22" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I22" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K22" s="28" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Týden 18</t>
         </is>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="27">
         <f>'Rozpis podle pokojů'!B24</f>
         <v/>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="27">
         <f>'Rozpis podle pokojů'!C24</f>
         <v/>
       </c>
-      <c r="D23" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E23" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G23" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H23" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I23" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J23" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K23" s="27" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J23" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K23" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -4122,105 +4058,105 @@
           <t>Týden 19</t>
         </is>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="22">
         <f>'Rozpis podle pokojů'!B25</f>
         <v/>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="22">
         <f>'Rozpis podle pokojů'!C25</f>
         <v/>
       </c>
-      <c r="D24" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G24" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H24" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I24" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K24" s="28" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K24" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Týden 20</t>
         </is>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="27">
         <f>'Rozpis podle pokojů'!B26</f>
         <v/>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="27">
         <f>'Rozpis podle pokojů'!C26</f>
         <v/>
       </c>
-      <c r="D25" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F25" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G25" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H25" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I25" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J25" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K25" s="27" t="inlineStr">
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J25" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K25" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -4232,105 +4168,105 @@
           <t>Týden 21</t>
         </is>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="22">
         <f>'Rozpis podle pokojů'!B27</f>
         <v/>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="22">
         <f>'Rozpis podle pokojů'!C27</f>
         <v/>
       </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G26" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H26" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I26" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K26" s="28" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Týden 22</t>
         </is>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="27">
         <f>'Rozpis podle pokojů'!B28</f>
         <v/>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="27">
         <f>'Rozpis podle pokojů'!C28</f>
         <v/>
       </c>
-      <c r="D27" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E27" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F27" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G27" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H27" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I27" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J27" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K27" s="27" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K27" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -4342,105 +4278,105 @@
           <t>Týden 23</t>
         </is>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="22">
         <f>'Rozpis podle pokojů'!B29</f>
         <v/>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="22">
         <f>'Rozpis podle pokojů'!C29</f>
         <v/>
       </c>
-      <c r="D28" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G28" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I28" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K28" s="28" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K28" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Týden 24</t>
         </is>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="27">
         <f>'Rozpis podle pokojů'!B30</f>
         <v/>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="27">
         <f>'Rozpis podle pokojů'!C30</f>
         <v/>
       </c>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F29" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G29" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H29" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I29" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J29" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K29" s="27" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J29" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K29" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -4452,105 +4388,105 @@
           <t>Týden 25</t>
         </is>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="22">
         <f>'Rozpis podle pokojů'!B31</f>
         <v/>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="22">
         <f>'Rozpis podle pokojů'!C31</f>
         <v/>
       </c>
-      <c r="D30" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G30" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I30" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K30" s="28" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G30" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Týden 26</t>
         </is>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="27">
         <f>'Rozpis podle pokojů'!B32</f>
         <v/>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="27">
         <f>'Rozpis podle pokojů'!C32</f>
         <v/>
       </c>
-      <c r="D31" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E31" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F31" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G31" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H31" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I31" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J31" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K31" s="27" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F31" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J31" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K31" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -4562,105 +4498,105 @@
           <t>Týden 27</t>
         </is>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="22">
         <f>'Rozpis podle pokojů'!B33</f>
         <v/>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="22">
         <f>'Rozpis podle pokojů'!C33</f>
         <v/>
       </c>
-      <c r="D32" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E32" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G32" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I32" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J32" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K32" s="28" t="inlineStr">
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K32" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Týden 28</t>
         </is>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="27">
         <f>'Rozpis podle pokojů'!B34</f>
         <v/>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="27">
         <f>'Rozpis podle pokojů'!C34</f>
         <v/>
       </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F33" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G33" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H33" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I33" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J33" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K33" s="27" t="inlineStr">
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K33" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -4672,105 +4608,105 @@
           <t>Týden 29</t>
         </is>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="22">
         <f>'Rozpis podle pokojů'!B35</f>
         <v/>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="22">
         <f>'Rozpis podle pokojů'!C35</f>
         <v/>
       </c>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G34" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H34" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I34" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J34" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K34" s="28" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F34" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G34" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Týden 30</t>
         </is>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="27">
         <f>'Rozpis podle pokojů'!B36</f>
         <v/>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="27">
         <f>'Rozpis podle pokojů'!C36</f>
         <v/>
       </c>
-      <c r="D35" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E35" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F35" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G35" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H35" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I35" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J35" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K35" s="27" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K35" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -4782,105 +4718,105 @@
           <t>Týden 31</t>
         </is>
       </c>
-      <c r="B36" s="24">
+      <c r="B36" s="22">
         <f>'Rozpis podle pokojů'!B37</f>
         <v/>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="22">
         <f>'Rozpis podle pokojů'!C37</f>
         <v/>
       </c>
-      <c r="D36" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E36" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F36" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G36" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I36" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J36" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K36" s="28" t="inlineStr">
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Týden 32</t>
         </is>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="27">
         <f>'Rozpis podle pokojů'!B38</f>
         <v/>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="27">
         <f>'Rozpis podle pokojů'!C38</f>
         <v/>
       </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F37" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G37" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H37" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I37" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J37" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K37" s="27" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K37" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -4892,105 +4828,105 @@
           <t>Týden 33</t>
         </is>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="22">
         <f>'Rozpis podle pokojů'!B39</f>
         <v/>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="22">
         <f>'Rozpis podle pokojů'!C39</f>
         <v/>
       </c>
-      <c r="D38" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E38" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G38" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H38" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I38" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J38" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K38" s="28" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F38" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Týden 34</t>
         </is>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="27">
         <f>'Rozpis podle pokojů'!B40</f>
         <v/>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="27">
         <f>'Rozpis podle pokojů'!C40</f>
         <v/>
       </c>
-      <c r="D39" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E39" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F39" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G39" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H39" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I39" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J39" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K39" s="27" t="inlineStr">
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F39" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I39" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J39" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K39" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -5002,105 +4938,105 @@
           <t>Týden 35</t>
         </is>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="22">
         <f>'Rozpis podle pokojů'!B41</f>
         <v/>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="22">
         <f>'Rozpis podle pokojů'!C41</f>
         <v/>
       </c>
-      <c r="D40" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E40" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F40" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H40" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I40" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J40" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K40" s="28" t="inlineStr">
+      <c r="D40" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K40" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>Týden 36</t>
         </is>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="27">
         <f>'Rozpis podle pokojů'!B42</f>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="27">
         <f>'Rozpis podle pokojů'!C42</f>
         <v/>
       </c>
-      <c r="D41" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F41" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G41" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H41" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I41" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J41" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K41" s="27" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G41" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I41" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J41" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K41" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -5112,105 +5048,105 @@
           <t>Týden 37</t>
         </is>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="22">
         <f>'Rozpis podle pokojů'!B43</f>
         <v/>
       </c>
-      <c r="C42" s="24">
+      <c r="C42" s="22">
         <f>'Rozpis podle pokojů'!C43</f>
         <v/>
       </c>
-      <c r="D42" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G42" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H42" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I42" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J42" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K42" s="28" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K42" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Týden 38</t>
         </is>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="27">
         <f>'Rozpis podle pokojů'!B44</f>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="27">
         <f>'Rozpis podle pokojů'!C44</f>
         <v/>
       </c>
-      <c r="D43" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E43" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F43" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G43" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H43" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I43" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J43" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K43" s="27" t="inlineStr">
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I43" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J43" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K43" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -5222,105 +5158,105 @@
           <t>Týden 39</t>
         </is>
       </c>
-      <c r="B44" s="24">
+      <c r="B44" s="22">
         <f>'Rozpis podle pokojů'!B45</f>
         <v/>
       </c>
-      <c r="C44" s="24">
+      <c r="C44" s="22">
         <f>'Rozpis podle pokojů'!C45</f>
         <v/>
       </c>
-      <c r="D44" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E44" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F44" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G44" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H44" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I44" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J44" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K44" s="28" t="inlineStr">
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K44" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>Týden 40</t>
         </is>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="27">
         <f>'Rozpis podle pokojů'!B46</f>
         <v/>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="27">
         <f>'Rozpis podle pokojů'!C46</f>
         <v/>
       </c>
-      <c r="D45" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F45" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G45" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H45" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I45" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J45" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K45" s="27" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G45" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I45" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J45" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K45" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -5332,105 +5268,105 @@
           <t>Týden 41</t>
         </is>
       </c>
-      <c r="B46" s="24">
+      <c r="B46" s="22">
         <f>'Rozpis podle pokojů'!B47</f>
         <v/>
       </c>
-      <c r="C46" s="24">
+      <c r="C46" s="22">
         <f>'Rozpis podle pokojů'!C47</f>
         <v/>
       </c>
-      <c r="D46" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G46" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H46" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I46" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J46" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K46" s="28" t="inlineStr">
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F46" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G46" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K46" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Týden 42</t>
         </is>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="27">
         <f>'Rozpis podle pokojů'!B48</f>
         <v/>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="27">
         <f>'Rozpis podle pokojů'!C48</f>
         <v/>
       </c>
-      <c r="D47" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E47" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F47" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G47" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H47" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I47" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J47" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K47" s="27" t="inlineStr">
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I47" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J47" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K47" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -5442,105 +5378,105 @@
           <t>Týden 43</t>
         </is>
       </c>
-      <c r="B48" s="24">
+      <c r="B48" s="22">
         <f>'Rozpis podle pokojů'!B49</f>
         <v/>
       </c>
-      <c r="C48" s="24">
+      <c r="C48" s="22">
         <f>'Rozpis podle pokojů'!C49</f>
         <v/>
       </c>
-      <c r="D48" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E48" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F48" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G48" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H48" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I48" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J48" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K48" s="28" t="inlineStr">
+      <c r="D48" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Týden 44</t>
         </is>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="27">
         <f>'Rozpis podle pokojů'!B50</f>
         <v/>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="27">
         <f>'Rozpis podle pokojů'!C50</f>
         <v/>
       </c>
-      <c r="D49" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F49" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G49" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H49" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I49" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J49" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K49" s="27" t="inlineStr">
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G49" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I49" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J49" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K49" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -5552,105 +5488,105 @@
           <t>Týden 45</t>
         </is>
       </c>
-      <c r="B50" s="24">
+      <c r="B50" s="22">
         <f>'Rozpis podle pokojů'!B51</f>
         <v/>
       </c>
-      <c r="C50" s="24">
+      <c r="C50" s="22">
         <f>'Rozpis podle pokojů'!C51</f>
         <v/>
       </c>
-      <c r="D50" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F50" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G50" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H50" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I50" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J50" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K50" s="28" t="inlineStr">
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F50" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K50" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>Týden 46</t>
         </is>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="27">
         <f>'Rozpis podle pokojů'!B52</f>
         <v/>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="27">
         <f>'Rozpis podle pokojů'!C52</f>
         <v/>
       </c>
-      <c r="D51" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E51" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F51" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G51" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H51" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I51" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K51" s="27" t="inlineStr">
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F51" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I51" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J51" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K51" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -5662,105 +5598,105 @@
           <t>Týden 47</t>
         </is>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="22">
         <f>'Rozpis podle pokojů'!B53</f>
         <v/>
       </c>
-      <c r="C52" s="24">
+      <c r="C52" s="22">
         <f>'Rozpis podle pokojů'!C53</f>
         <v/>
       </c>
-      <c r="D52" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E52" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F52" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G52" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H52" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I52" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J52" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
+      <c r="D52" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K52" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Týden 48</t>
         </is>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="27">
         <f>'Rozpis podle pokojů'!B54</f>
         <v/>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="27">
         <f>'Rozpis podle pokojů'!C54</f>
         <v/>
       </c>
-      <c r="D53" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E53" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G53" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H53" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I53" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J53" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K53" s="27" t="inlineStr">
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G53" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I53" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J53" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K53" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -5772,105 +5708,105 @@
           <t>Týden 49</t>
         </is>
       </c>
-      <c r="B54" s="24">
+      <c r="B54" s="22">
         <f>'Rozpis podle pokojů'!B55</f>
         <v/>
       </c>
-      <c r="C54" s="24">
+      <c r="C54" s="22">
         <f>'Rozpis podle pokojů'!C55</f>
         <v/>
       </c>
-      <c r="D54" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="G54" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="H54" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I54" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J54" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="inlineStr">
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="F54" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="G54" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J54" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K54" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>Týden 50</t>
         </is>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="27">
         <f>'Rozpis podle pokojů'!B56</f>
         <v/>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="27">
         <f>'Rozpis podle pokojů'!C56</f>
         <v/>
       </c>
-      <c r="D55" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="E55" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="F55" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="G55" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="H55" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I55" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K55" s="27" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="F55" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="H55" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I55" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J55" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K55" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -5882,105 +5818,105 @@
           <t>Týden 51</t>
         </is>
       </c>
-      <c r="B56" s="24">
+      <c r="B56" s="22">
         <f>'Rozpis podle pokojů'!B57</f>
         <v/>
       </c>
-      <c r="C56" s="24">
+      <c r="C56" s="22">
         <f>'Rozpis podle pokojů'!C57</f>
         <v/>
       </c>
-      <c r="D56" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="E56" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="F56" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="G56" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="H56" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="I56" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="J56" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="inlineStr">
+      <c r="D56" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="H56" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="J56" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="K56" s="26" t="inlineStr">
         <is>
           <t>Pokoj 4</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Týden 52</t>
         </is>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="27">
         <f>'Rozpis podle pokojů'!B58</f>
         <v/>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="27">
         <f>'Rozpis podle pokojů'!C58</f>
         <v/>
       </c>
-      <c r="D57" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="F57" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="G57" s="27" t="inlineStr">
-        <is>
-          <t>Pokoj 3</t>
-        </is>
-      </c>
-      <c r="H57" s="26" t="inlineStr">
-        <is>
-          <t>Pokoj 2</t>
-        </is>
-      </c>
-      <c r="I57" s="25" t="inlineStr">
-        <is>
-          <t>Pokoj 1</t>
-        </is>
-      </c>
-      <c r="J57" s="28" t="inlineStr">
-        <is>
-          <t>Pokoj 4</t>
-        </is>
-      </c>
-      <c r="K57" s="27" t="inlineStr">
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="G57" s="25" t="inlineStr">
+        <is>
+          <t>Pokoj 3</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
+        <is>
+          <t>Pokoj 2</t>
+        </is>
+      </c>
+      <c r="I57" s="23" t="inlineStr">
+        <is>
+          <t>Pokoj 1</t>
+        </is>
+      </c>
+      <c r="J57" s="26" t="inlineStr">
+        <is>
+          <t>Pokoj 4</t>
+        </is>
+      </c>
+      <c r="K57" s="25" t="inlineStr">
         <is>
           <t>Pokoj 3</t>
         </is>
@@ -6005,7 +5941,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -6030,523 +5966,523 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>🧹  SCHODY   —   (Společné prostory domu)</t>
         </is>
       </c>
-      <c r="B4" s="31" t="n"/>
-      <c r="C4" s="31" t="n"/>
-      <c r="D4" s="31" t="n"/>
-      <c r="E4" s="31" t="n"/>
-      <c r="F4" s="32" t="n"/>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="29" t="n"/>
+      <c r="E4" s="29" t="n"/>
+      <c r="F4" s="30" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Zamést a vytřít celé naše patro (prostor chodby přímo před bytem).</t>
         </is>
       </c>
-      <c r="F5" s="35" t="n"/>
+      <c r="F5" s="33" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Zamést a vytřít dvoje schody směrem dolů včetně mezipatra.</t>
         </is>
       </c>
-      <c r="F6" s="35" t="n"/>
+      <c r="F6" s="33" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Zkontrolovat, že na mezipatře / schodech nezůstaly žádné odpadky, letáky nebo kamínky.</t>
         </is>
       </c>
-      <c r="F7" s="35" t="n"/>
+      <c r="F7" s="33" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Doporučený čas splnění: pátek odpoledne nebo sobota dopoledne.</t>
         </is>
       </c>
-      <c r="F8" s="35" t="n"/>
+      <c r="F8" s="33" t="n"/>
     </row>
     <row r="9" ht="6" customHeight="1">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="37" t="n"/>
-      <c r="C9" s="37" t="n"/>
-      <c r="D9" s="37" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="38" t="n"/>
+      <c r="A9" s="34" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="36" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>🍳  KUCHYŇ   —   (Společná zóna vaření)</t>
         </is>
       </c>
-      <c r="B11" s="40" t="n"/>
-      <c r="C11" s="40" t="n"/>
-      <c r="D11" s="40" t="n"/>
-      <c r="E11" s="40" t="n"/>
-      <c r="F11" s="41" t="n"/>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="39" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>Starat se o kuchyňskou linku, dřez a varnou desku (otírat mastnotu a drobky).</t>
         </is>
       </c>
-      <c r="F12" s="42" t="n"/>
+      <c r="F12" s="40" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Průběžně vyndávat umytou myčku a uklízet nádobí do skříněk.</t>
         </is>
       </c>
-      <c r="F13" s="42" t="n"/>
+      <c r="F13" s="40" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>Zapnout myčku, jakmile se naplní (nenechávat špinavé nádobí hromadit ve dřezu).</t>
         </is>
       </c>
-      <c r="F14" s="42" t="n"/>
+      <c r="F14" s="40" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Pravidelně zametat a vytírat podlahu v kuchyni (dle potřeby i v týdnu, min. 1× důkladně na závěr).</t>
         </is>
       </c>
-      <c r="F15" s="42" t="n"/>
+      <c r="F15" s="40" t="n"/>
     </row>
     <row r="16" ht="6" customHeight="1">
-      <c r="A16" s="43" t="n"/>
-      <c r="B16" s="44" t="n"/>
-      <c r="C16" s="44" t="n"/>
-      <c r="D16" s="44" t="n"/>
-      <c r="E16" s="44" t="n"/>
-      <c r="F16" s="45" t="n"/>
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="42" t="n"/>
+      <c r="D16" s="42" t="n"/>
+      <c r="E16" s="42" t="n"/>
+      <c r="F16" s="43" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>🗑️  ODPADKY   —   (Čistý a voňavý byt)</t>
         </is>
       </c>
-      <c r="B18" s="47" t="n"/>
-      <c r="C18" s="47" t="n"/>
-      <c r="D18" s="47" t="n"/>
-      <c r="E18" s="47" t="n"/>
-      <c r="F18" s="48" t="n"/>
+      <c r="B18" s="45" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="46" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Pravidelně vynášet pytle se směsným odpadem, jakmile jsou plné (nečekat na přetečení).</t>
         </is>
       </c>
-      <c r="F19" s="49" t="n"/>
+      <c r="F19" s="47" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Po vynesení koše VŽDY ihned nasadit nový čistý pytel!</t>
         </is>
       </c>
-      <c r="F20" s="49" t="n"/>
+      <c r="F20" s="47" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Vynášet tříděný odpad (plast, papír, plechovky, sklo) do příslušných kontejnerů.</t>
         </is>
       </c>
-      <c r="F21" s="49" t="n"/>
+      <c r="F21" s="47" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Udržovat prostor kolem odpadkových košů čistý (žádné skvrny ani kapky na podlaze).</t>
         </is>
       </c>
-      <c r="F22" s="49" t="n"/>
+      <c r="F22" s="47" t="n"/>
     </row>
     <row r="23" ht="6" customHeight="1">
-      <c r="A23" s="50" t="n"/>
-      <c r="B23" s="51" t="n"/>
-      <c r="C23" s="51" t="n"/>
-      <c r="D23" s="51" t="n"/>
-      <c r="E23" s="51" t="n"/>
-      <c r="F23" s="52" t="n"/>
+      <c r="A23" s="48" t="n"/>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="50" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="53" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t>🛋️  PŘEDSÍŇ   —   (Vstupní společný prostor)</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="54" t="n"/>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="55" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="53" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Zametat a vytírat podlahu v předsíni (zejména rohožku, vstup a prostor botníku).</t>
         </is>
       </c>
-      <c r="F26" s="56" t="n"/>
+      <c r="F26" s="54" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B27" s="34" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Urovnat boty v botníku a věšáky u vchodu.</t>
         </is>
       </c>
-      <c r="F27" s="56" t="n"/>
+      <c r="F27" s="54" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Stlát gauč / postel v předsíni, složit deky a polštáře, udržovat estetický pořádek.</t>
         </is>
       </c>
-      <c r="F28" s="56" t="n"/>
+      <c r="F28" s="54" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>Otřít prach na botníku a povrchu skříněk.</t>
         </is>
       </c>
-      <c r="F29" s="56" t="n"/>
+      <c r="F29" s="54" t="n"/>
     </row>
     <row r="30" ht="6" customHeight="1">
-      <c r="A30" s="57" t="n"/>
-      <c r="B30" s="58" t="n"/>
-      <c r="C30" s="58" t="n"/>
-      <c r="D30" s="58" t="n"/>
-      <c r="E30" s="58" t="n"/>
-      <c r="F30" s="59" t="n"/>
+      <c r="A30" s="55" t="n"/>
+      <c r="B30" s="56" t="n"/>
+      <c r="C30" s="56" t="n"/>
+      <c r="D30" s="56" t="n"/>
+      <c r="E30" s="56" t="n"/>
+      <c r="F30" s="57" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="60" t="inlineStr">
+      <c r="A32" s="58" t="inlineStr">
         <is>
           <t>🚿  KOUPELNA (Privátní: P1+P2 nebo P3+P4)   —   (Pokoje 1 &amp; 2 mají svou • Pokoje 3 &amp; 4 mají svou)</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="32" t="n"/>
+      <c r="B32" s="29" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="30" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B33" s="34" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>Vyčistit umyvadlo, baterii a zrcadlo (odstranit zaschlou vodu a zubní pastu).</t>
         </is>
       </c>
-      <c r="F33" s="35" t="n"/>
+      <c r="F33" s="33" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B34" s="34" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Důkladně vymýt sprchový kout / vanu a odstranit vlasy ze sítka/odpadu.</t>
         </is>
       </c>
-      <c r="F34" s="35" t="n"/>
+      <c r="F34" s="33" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>Vytřít podlahu v koupelně.</t>
         </is>
       </c>
-      <c r="F35" s="35" t="n"/>
+      <c r="F35" s="33" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B36" s="34" t="inlineStr">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Zkontrolovat předložku a vyvětrat vlhkost.</t>
         </is>
       </c>
-      <c r="F36" s="35" t="n"/>
+      <c r="F36" s="33" t="n"/>
     </row>
     <row r="37" ht="6" customHeight="1">
-      <c r="A37" s="36" t="n"/>
-      <c r="B37" s="37" t="n"/>
-      <c r="C37" s="37" t="n"/>
-      <c r="D37" s="37" t="n"/>
-      <c r="E37" s="37" t="n"/>
-      <c r="F37" s="38" t="n"/>
+      <c r="A37" s="34" t="n"/>
+      <c r="B37" s="35" t="n"/>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="35" t="n"/>
+      <c r="E37" s="35" t="n"/>
+      <c r="F37" s="36" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="61" t="inlineStr">
+      <c r="A39" s="59" t="inlineStr">
         <is>
           <t>🚽  ZÁCHOD (Privátní: P1+P2 nebo P3+P4)   —   (Pokoje 1 &amp; 2 mají své • Pokoje 3 &amp; 4 mají své)</t>
         </is>
       </c>
-      <c r="B39" s="62" t="n"/>
-      <c r="C39" s="62" t="n"/>
-      <c r="D39" s="62" t="n"/>
-      <c r="E39" s="62" t="n"/>
-      <c r="F39" s="63" t="n"/>
+      <c r="B39" s="60" t="n"/>
+      <c r="C39" s="60" t="n"/>
+      <c r="D39" s="60" t="n"/>
+      <c r="E39" s="60" t="n"/>
+      <c r="F39" s="61" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B40" s="34" t="inlineStr">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="inlineStr">
         <is>
           <t>Důkladně vyčistit mísu WC čističem a štětkou.</t>
         </is>
       </c>
-      <c r="F40" s="64" t="n"/>
+      <c r="F40" s="62" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B41" s="34" t="inlineStr">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>Dezinfekčním sprejem/hadříkem otřít prkénko (shora i zespodu), splachovadlo a okolí.</t>
         </is>
       </c>
-      <c r="F41" s="64" t="n"/>
+      <c r="F41" s="62" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B42" s="34" t="inlineStr">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B42" s="32" t="inlineStr">
         <is>
           <t>Zkontrolovat stav toaletního papíru a včas doplnit náhradní ruličky.</t>
         </is>
       </c>
-      <c r="F42" s="64" t="n"/>
+      <c r="F42" s="62" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="33" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="B43" s="34" t="inlineStr">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>Vytřít podlahu na záchodě.</t>
         </is>
       </c>
-      <c r="F43" s="64" t="n"/>
+      <c r="F43" s="62" t="n"/>
     </row>
     <row r="44" ht="6" customHeight="1">
-      <c r="A44" s="65" t="n"/>
-      <c r="B44" s="66" t="n"/>
-      <c r="C44" s="66" t="n"/>
-      <c r="D44" s="66" t="n"/>
-      <c r="E44" s="66" t="n"/>
-      <c r="F44" s="67" t="n"/>
+      <c r="A44" s="63" t="n"/>
+      <c r="B44" s="64" t="n"/>
+      <c r="C44" s="64" t="n"/>
+      <c r="D44" s="64" t="n"/>
+      <c r="E44" s="64" t="n"/>
+      <c r="F44" s="65" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="68" t="inlineStr">
+      <c r="A46" s="66" t="inlineStr">
         <is>
           <t>⚖️ ZLATÁ PRAVIDLA SPOLUBYDLENÍ</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="69" t="inlineStr">
+      <c r="A47" s="67" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="B47" s="70" t="inlineStr">
+      <c r="B47" s="68" t="inlineStr">
         <is>
           <t>Předání služeb:</t>
         </is>
       </c>
-      <c r="C47" s="71" t="inlineStr">
+      <c r="C47" s="69" t="inlineStr">
         <is>
           <t>Služba se oficiálně předává v NEDĚLI do 20:00 (do té doby je vše hotovo).</t>
         </is>
       </c>
-      <c r="D47" s="72" t="n"/>
-      <c r="E47" s="72" t="n"/>
-      <c r="F47" s="72" t="n"/>
+      <c r="D47" s="70" t="n"/>
+      <c r="E47" s="70" t="n"/>
+      <c r="F47" s="70" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="69" t="inlineStr">
+      <c r="A48" s="67" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="B48" s="70" t="inlineStr">
+      <c r="B48" s="68" t="inlineStr">
         <is>
           <t>Nepřítomnost:</t>
         </is>
       </c>
-      <c r="C48" s="71" t="inlineStr">
+      <c r="C48" s="69" t="inlineStr">
         <is>
           <t>Když někdo odjíždí na týden pryč, je jeho povinností si zajistit výměnu s jiným pokojem.</t>
         </is>
       </c>
-      <c r="D48" s="72" t="n"/>
-      <c r="E48" s="72" t="n"/>
-      <c r="F48" s="72" t="n"/>
+      <c r="D48" s="70" t="n"/>
+      <c r="E48" s="70" t="n"/>
+      <c r="F48" s="70" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="69" t="inlineStr">
+      <c r="A49" s="67" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="B49" s="70" t="inlineStr">
+      <c r="B49" s="68" t="inlineStr">
         <is>
           <t>Průběžný pořádek:</t>
         </is>
       </c>
-      <c r="C49" s="71" t="inlineStr">
+      <c r="C49" s="69" t="inlineStr">
         <is>
           <t>Služba neuklízí cizí nepořádek! Každý po sobě ihned utře linku, když něco rozlije, a umyje své věci.</t>
         </is>
       </c>
-      <c r="D49" s="72" t="n"/>
-      <c r="E49" s="72" t="n"/>
-      <c r="F49" s="72" t="n"/>
+      <c r="D49" s="70" t="n"/>
+      <c r="E49" s="70" t="n"/>
+      <c r="F49" s="70" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="69" t="inlineStr">
+      <c r="A50" s="67" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="B50" s="70" t="inlineStr">
-        <is>
-          <t>Spotřební materiál:</t>
-        </is>
-      </c>
-      <c r="C50" s="71" t="inlineStr">
-        <is>
-          <t>Když dochází jar, tablety do myčky, WC gel nebo pytle, napíše se to do skupiny a koupí ze společného.</t>
-        </is>
-      </c>
-      <c r="D50" s="72" t="n"/>
-      <c r="E50" s="72" t="n"/>
-      <c r="F50" s="72" t="n"/>
+      <c r="B50" s="68" t="inlineStr">
+        <is>
+          <t>Spotřební materiál a chemie:</t>
+        </is>
+      </c>
+      <c r="C50" s="69" t="inlineStr">
+        <is>
+          <t>Když dochází jar, tablety do myčky, WC gel, toaletní papír nebo pytle do koše, tak to koupíš a hodíš do SettleUp.</t>
+        </is>
+      </c>
+      <c r="D50" s="70" t="n"/>
+      <c r="E50" s="70" t="n"/>
+      <c r="F50" s="70" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="37">

--- a/rozpis_sluzeb_byt.xlsx
+++ b/rozpis_sluzeb_byt.xlsx
@@ -5940,7 +5940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="C49" s="69" t="inlineStr">
         <is>
-          <t>Služba neuklízí cizí nepořádek! Každý po sobě ihned utře linku, když něco rozlije, a umyje své věci.</t>
+          <t>Služba neuklízí cizí nepořádek! Každý po sobě ihned utře linku, když něco rozlije, a udržuje pořádek.</t>
         </is>
       </c>
       <c r="D49" s="70" t="n"/>
@@ -6472,20 +6472,40 @@
       </c>
       <c r="B50" s="68" t="inlineStr">
         <is>
-          <t>Spotřební materiál a chemie:</t>
+          <t>Žádné nádobí ve dřezu:</t>
         </is>
       </c>
       <c r="C50" s="69" t="inlineStr">
         <is>
-          <t>Když dochází jar, tablety do myčky, WC gel, toaletní papír nebo pytle do koše, tak to koupíš a hodíš do SettleUp.</t>
+          <t>Ve dřezu nesmí zůstávat nádobí – plný dřez se nedá používat. Při plné myčce odložit vedle na linku a pak do myčky, nebo hned umýt.</t>
         </is>
       </c>
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
     </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="67" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B51" s="68" t="inlineStr">
+        <is>
+          <t>Spotřební materiál a chemie:</t>
+        </is>
+      </c>
+      <c r="C51" s="69" t="inlineStr">
+        <is>
+          <t>Když dochází jar, tablety do myčky, WC gel, toaletní papír nebo pytle do koše, tak to koupíš a hodíš do SettleUp.</t>
+        </is>
+      </c>
+      <c r="D51" s="70" t="n"/>
+      <c r="E51" s="70" t="n"/>
+      <c r="F51" s="70" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="38">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="A46:F46"/>
@@ -6519,6 +6539,7 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="C51:F51"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="A25:F25"/>

--- a/rozpis_sluzeb_byt.xlsx
+++ b/rozpis_sluzeb_byt.xlsx
@@ -1123,10 +1123,9 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Týden 1</t>
-        </is>
+      <c r="A7" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B7)</f>
+        <v/>
       </c>
       <c r="B7" s="12">
         <f>$B$4 + (0*7)</f>
@@ -1158,10 +1157,9 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Týden 2</t>
-        </is>
+      <c r="A8" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B8)</f>
+        <v/>
       </c>
       <c r="B8" s="15">
         <f>$B$4 + (1*7)</f>
@@ -1193,10 +1191,9 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Týden 3</t>
-        </is>
+      <c r="A9" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B9)</f>
+        <v/>
       </c>
       <c r="B9" s="12">
         <f>$B$4 + (2*7)</f>
@@ -1228,10 +1225,9 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Týden 4</t>
-        </is>
+      <c r="A10" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B10)</f>
+        <v/>
       </c>
       <c r="B10" s="15">
         <f>$B$4 + (3*7)</f>
@@ -1263,10 +1259,9 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Týden 5</t>
-        </is>
+      <c r="A11" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B11)</f>
+        <v/>
       </c>
       <c r="B11" s="12">
         <f>$B$4 + (4*7)</f>
@@ -1298,10 +1293,9 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Týden 6</t>
-        </is>
+      <c r="A12" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B12)</f>
+        <v/>
       </c>
       <c r="B12" s="15">
         <f>$B$4 + (5*7)</f>
@@ -1333,10 +1327,9 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Týden 7</t>
-        </is>
+      <c r="A13" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B13)</f>
+        <v/>
       </c>
       <c r="B13" s="12">
         <f>$B$4 + (6*7)</f>
@@ -1368,10 +1361,9 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Týden 8</t>
-        </is>
+      <c r="A14" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B14)</f>
+        <v/>
       </c>
       <c r="B14" s="15">
         <f>$B$4 + (7*7)</f>
@@ -1403,10 +1395,9 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Týden 9</t>
-        </is>
+      <c r="A15" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B15)</f>
+        <v/>
       </c>
       <c r="B15" s="12">
         <f>$B$4 + (8*7)</f>
@@ -1438,10 +1429,9 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Týden 10</t>
-        </is>
+      <c r="A16" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B16)</f>
+        <v/>
       </c>
       <c r="B16" s="15">
         <f>$B$4 + (9*7)</f>
@@ -1473,10 +1463,9 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Týden 11</t>
-        </is>
+      <c r="A17" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B17)</f>
+        <v/>
       </c>
       <c r="B17" s="12">
         <f>$B$4 + (10*7)</f>
@@ -1508,10 +1497,9 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Týden 12</t>
-        </is>
+      <c r="A18" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B18)</f>
+        <v/>
       </c>
       <c r="B18" s="15">
         <f>$B$4 + (11*7)</f>
@@ -1543,10 +1531,9 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Týden 13</t>
-        </is>
+      <c r="A19" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B19)</f>
+        <v/>
       </c>
       <c r="B19" s="12">
         <f>$B$4 + (12*7)</f>
@@ -1578,10 +1565,9 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Týden 14</t>
-        </is>
+      <c r="A20" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B20)</f>
+        <v/>
       </c>
       <c r="B20" s="15">
         <f>$B$4 + (13*7)</f>
@@ -1613,10 +1599,9 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Týden 15</t>
-        </is>
+      <c r="A21" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B21)</f>
+        <v/>
       </c>
       <c r="B21" s="12">
         <f>$B$4 + (14*7)</f>
@@ -1648,10 +1633,9 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Týden 16</t>
-        </is>
+      <c r="A22" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B22)</f>
+        <v/>
       </c>
       <c r="B22" s="15">
         <f>$B$4 + (15*7)</f>
@@ -1683,10 +1667,9 @@
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Týden 17</t>
-        </is>
+      <c r="A23" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B23)</f>
+        <v/>
       </c>
       <c r="B23" s="12">
         <f>$B$4 + (16*7)</f>
@@ -1718,10 +1701,9 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Týden 18</t>
-        </is>
+      <c r="A24" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B24)</f>
+        <v/>
       </c>
       <c r="B24" s="15">
         <f>$B$4 + (17*7)</f>
@@ -1753,10 +1735,9 @@
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Týden 19</t>
-        </is>
+      <c r="A25" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B25)</f>
+        <v/>
       </c>
       <c r="B25" s="12">
         <f>$B$4 + (18*7)</f>
@@ -1788,10 +1769,9 @@
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Týden 20</t>
-        </is>
+      <c r="A26" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B26)</f>
+        <v/>
       </c>
       <c r="B26" s="15">
         <f>$B$4 + (19*7)</f>
@@ -1823,10 +1803,9 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Týden 21</t>
-        </is>
+      <c r="A27" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B27)</f>
+        <v/>
       </c>
       <c r="B27" s="12">
         <f>$B$4 + (20*7)</f>
@@ -1858,10 +1837,9 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Týden 22</t>
-        </is>
+      <c r="A28" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B28)</f>
+        <v/>
       </c>
       <c r="B28" s="15">
         <f>$B$4 + (21*7)</f>
@@ -1893,10 +1871,9 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Týden 23</t>
-        </is>
+      <c r="A29" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B29)</f>
+        <v/>
       </c>
       <c r="B29" s="12">
         <f>$B$4 + (22*7)</f>
@@ -1928,10 +1905,9 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>Týden 24</t>
-        </is>
+      <c r="A30" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B30)</f>
+        <v/>
       </c>
       <c r="B30" s="15">
         <f>$B$4 + (23*7)</f>
@@ -1963,10 +1939,9 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Týden 25</t>
-        </is>
+      <c r="A31" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B31)</f>
+        <v/>
       </c>
       <c r="B31" s="12">
         <f>$B$4 + (24*7)</f>
@@ -1998,10 +1973,9 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Týden 26</t>
-        </is>
+      <c r="A32" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B32)</f>
+        <v/>
       </c>
       <c r="B32" s="15">
         <f>$B$4 + (25*7)</f>
@@ -2033,10 +2007,9 @@
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Týden 27</t>
-        </is>
+      <c r="A33" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B33)</f>
+        <v/>
       </c>
       <c r="B33" s="12">
         <f>$B$4 + (26*7)</f>
@@ -2068,10 +2041,9 @@
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Týden 28</t>
-        </is>
+      <c r="A34" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B34)</f>
+        <v/>
       </c>
       <c r="B34" s="15">
         <f>$B$4 + (27*7)</f>
@@ -2103,10 +2075,9 @@
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Týden 29</t>
-        </is>
+      <c r="A35" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B35)</f>
+        <v/>
       </c>
       <c r="B35" s="12">
         <f>$B$4 + (28*7)</f>
@@ -2138,10 +2109,9 @@
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>Týden 30</t>
-        </is>
+      <c r="A36" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B36)</f>
+        <v/>
       </c>
       <c r="B36" s="15">
         <f>$B$4 + (29*7)</f>
@@ -2173,10 +2143,9 @@
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Týden 31</t>
-        </is>
+      <c r="A37" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B37)</f>
+        <v/>
       </c>
       <c r="B37" s="12">
         <f>$B$4 + (30*7)</f>
@@ -2208,10 +2177,9 @@
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>Týden 32</t>
-        </is>
+      <c r="A38" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B38)</f>
+        <v/>
       </c>
       <c r="B38" s="15">
         <f>$B$4 + (31*7)</f>
@@ -2243,10 +2211,9 @@
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Týden 33</t>
-        </is>
+      <c r="A39" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B39)</f>
+        <v/>
       </c>
       <c r="B39" s="12">
         <f>$B$4 + (32*7)</f>
@@ -2278,10 +2245,9 @@
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>Týden 34</t>
-        </is>
+      <c r="A40" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B40)</f>
+        <v/>
       </c>
       <c r="B40" s="15">
         <f>$B$4 + (33*7)</f>
@@ -2313,10 +2279,9 @@
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Týden 35</t>
-        </is>
+      <c r="A41" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B41)</f>
+        <v/>
       </c>
       <c r="B41" s="12">
         <f>$B$4 + (34*7)</f>
@@ -2348,10 +2313,9 @@
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>Týden 36</t>
-        </is>
+      <c r="A42" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B42)</f>
+        <v/>
       </c>
       <c r="B42" s="15">
         <f>$B$4 + (35*7)</f>
@@ -2383,10 +2347,9 @@
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>Týden 37</t>
-        </is>
+      <c r="A43" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B43)</f>
+        <v/>
       </c>
       <c r="B43" s="12">
         <f>$B$4 + (36*7)</f>
@@ -2418,10 +2381,9 @@
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>Týden 38</t>
-        </is>
+      <c r="A44" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B44)</f>
+        <v/>
       </c>
       <c r="B44" s="15">
         <f>$B$4 + (37*7)</f>
@@ -2453,10 +2415,9 @@
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>Týden 39</t>
-        </is>
+      <c r="A45" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B45)</f>
+        <v/>
       </c>
       <c r="B45" s="12">
         <f>$B$4 + (38*7)</f>
@@ -2488,10 +2449,9 @@
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>Týden 40</t>
-        </is>
+      <c r="A46" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B46)</f>
+        <v/>
       </c>
       <c r="B46" s="15">
         <f>$B$4 + (39*7)</f>
@@ -2523,10 +2483,9 @@
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>Týden 41</t>
-        </is>
+      <c r="A47" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B47)</f>
+        <v/>
       </c>
       <c r="B47" s="12">
         <f>$B$4 + (40*7)</f>
@@ -2558,10 +2517,9 @@
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>Týden 42</t>
-        </is>
+      <c r="A48" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B48)</f>
+        <v/>
       </c>
       <c r="B48" s="15">
         <f>$B$4 + (41*7)</f>
@@ -2593,10 +2551,9 @@
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Týden 43</t>
-        </is>
+      <c r="A49" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B49)</f>
+        <v/>
       </c>
       <c r="B49" s="12">
         <f>$B$4 + (42*7)</f>
@@ -2628,10 +2585,9 @@
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>Týden 44</t>
-        </is>
+      <c r="A50" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B50)</f>
+        <v/>
       </c>
       <c r="B50" s="15">
         <f>$B$4 + (43*7)</f>
@@ -2663,10 +2619,9 @@
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>Týden 45</t>
-        </is>
+      <c r="A51" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B51)</f>
+        <v/>
       </c>
       <c r="B51" s="12">
         <f>$B$4 + (44*7)</f>
@@ -2698,10 +2653,9 @@
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>Týden 46</t>
-        </is>
+      <c r="A52" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B52)</f>
+        <v/>
       </c>
       <c r="B52" s="15">
         <f>$B$4 + (45*7)</f>
@@ -2733,10 +2687,9 @@
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>Týden 47</t>
-        </is>
+      <c r="A53" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B53)</f>
+        <v/>
       </c>
       <c r="B53" s="12">
         <f>$B$4 + (46*7)</f>
@@ -2768,10 +2721,9 @@
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>Týden 48</t>
-        </is>
+      <c r="A54" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B54)</f>
+        <v/>
       </c>
       <c r="B54" s="15">
         <f>$B$4 + (47*7)</f>
@@ -2803,10 +2755,9 @@
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>Týden 49</t>
-        </is>
+      <c r="A55" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B55)</f>
+        <v/>
       </c>
       <c r="B55" s="12">
         <f>$B$4 + (48*7)</f>
@@ -2838,10 +2789,9 @@
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>Týden 50</t>
-        </is>
+      <c r="A56" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B56)</f>
+        <v/>
       </c>
       <c r="B56" s="15">
         <f>$B$4 + (49*7)</f>
@@ -2873,10 +2823,9 @@
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>Týden 51</t>
-        </is>
+      <c r="A57" s="11">
+        <f>"Týden " &amp; ISOWEEKNUM(B57)</f>
+        <v/>
       </c>
       <c r="B57" s="12">
         <f>$B$4 + (50*7)</f>
@@ -2908,10 +2857,9 @@
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>Týden 52</t>
-        </is>
+      <c r="A58" s="14">
+        <f>"Týden " &amp; ISOWEEKNUM(B58)</f>
+        <v/>
       </c>
       <c r="B58" s="15">
         <f>$B$4 + (51*7)</f>
@@ -3063,10 +3011,9 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Týden 1</t>
-        </is>
+      <c r="A6" s="11">
+        <f>'Rozpis podle pokojů'!A7</f>
+        <v/>
       </c>
       <c r="B6" s="22">
         <f>'Rozpis podle pokojů'!B7</f>
@@ -3118,10 +3065,9 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Týden 2</t>
-        </is>
+      <c r="A7" s="14">
+        <f>'Rozpis podle pokojů'!A8</f>
+        <v/>
       </c>
       <c r="B7" s="27">
         <f>'Rozpis podle pokojů'!B8</f>
@@ -3173,10 +3119,9 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Týden 3</t>
-        </is>
+      <c r="A8" s="11">
+        <f>'Rozpis podle pokojů'!A9</f>
+        <v/>
       </c>
       <c r="B8" s="22">
         <f>'Rozpis podle pokojů'!B9</f>
@@ -3228,10 +3173,9 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Týden 4</t>
-        </is>
+      <c r="A9" s="14">
+        <f>'Rozpis podle pokojů'!A10</f>
+        <v/>
       </c>
       <c r="B9" s="27">
         <f>'Rozpis podle pokojů'!B10</f>
@@ -3283,10 +3227,9 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Týden 5</t>
-        </is>
+      <c r="A10" s="11">
+        <f>'Rozpis podle pokojů'!A11</f>
+        <v/>
       </c>
       <c r="B10" s="22">
         <f>'Rozpis podle pokojů'!B11</f>
@@ -3338,10 +3281,9 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Týden 6</t>
-        </is>
+      <c r="A11" s="14">
+        <f>'Rozpis podle pokojů'!A12</f>
+        <v/>
       </c>
       <c r="B11" s="27">
         <f>'Rozpis podle pokojů'!B12</f>
@@ -3393,10 +3335,9 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Týden 7</t>
-        </is>
+      <c r="A12" s="11">
+        <f>'Rozpis podle pokojů'!A13</f>
+        <v/>
       </c>
       <c r="B12" s="22">
         <f>'Rozpis podle pokojů'!B13</f>
@@ -3448,10 +3389,9 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Týden 8</t>
-        </is>
+      <c r="A13" s="14">
+        <f>'Rozpis podle pokojů'!A14</f>
+        <v/>
       </c>
       <c r="B13" s="27">
         <f>'Rozpis podle pokojů'!B14</f>
@@ -3503,10 +3443,9 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Týden 9</t>
-        </is>
+      <c r="A14" s="11">
+        <f>'Rozpis podle pokojů'!A15</f>
+        <v/>
       </c>
       <c r="B14" s="22">
         <f>'Rozpis podle pokojů'!B15</f>
@@ -3558,10 +3497,9 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Týden 10</t>
-        </is>
+      <c r="A15" s="14">
+        <f>'Rozpis podle pokojů'!A16</f>
+        <v/>
       </c>
       <c r="B15" s="27">
         <f>'Rozpis podle pokojů'!B16</f>
@@ -3613,10 +3551,9 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Týden 11</t>
-        </is>
+      <c r="A16" s="11">
+        <f>'Rozpis podle pokojů'!A17</f>
+        <v/>
       </c>
       <c r="B16" s="22">
         <f>'Rozpis podle pokojů'!B17</f>
@@ -3668,10 +3605,9 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Týden 12</t>
-        </is>
+      <c r="A17" s="14">
+        <f>'Rozpis podle pokojů'!A18</f>
+        <v/>
       </c>
       <c r="B17" s="27">
         <f>'Rozpis podle pokojů'!B18</f>
@@ -3723,10 +3659,9 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Týden 13</t>
-        </is>
+      <c r="A18" s="11">
+        <f>'Rozpis podle pokojů'!A19</f>
+        <v/>
       </c>
       <c r="B18" s="22">
         <f>'Rozpis podle pokojů'!B19</f>
@@ -3778,10 +3713,9 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Týden 14</t>
-        </is>
+      <c r="A19" s="14">
+        <f>'Rozpis podle pokojů'!A20</f>
+        <v/>
       </c>
       <c r="B19" s="27">
         <f>'Rozpis podle pokojů'!B20</f>
@@ -3833,10 +3767,9 @@
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Týden 15</t>
-        </is>
+      <c r="A20" s="11">
+        <f>'Rozpis podle pokojů'!A21</f>
+        <v/>
       </c>
       <c r="B20" s="22">
         <f>'Rozpis podle pokojů'!B21</f>
@@ -3888,10 +3821,9 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Týden 16</t>
-        </is>
+      <c r="A21" s="14">
+        <f>'Rozpis podle pokojů'!A22</f>
+        <v/>
       </c>
       <c r="B21" s="27">
         <f>'Rozpis podle pokojů'!B22</f>
@@ -3943,10 +3875,9 @@
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Týden 17</t>
-        </is>
+      <c r="A22" s="11">
+        <f>'Rozpis podle pokojů'!A23</f>
+        <v/>
       </c>
       <c r="B22" s="22">
         <f>'Rozpis podle pokojů'!B23</f>
@@ -3998,10 +3929,9 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Týden 18</t>
-        </is>
+      <c r="A23" s="14">
+        <f>'Rozpis podle pokojů'!A24</f>
+        <v/>
       </c>
       <c r="B23" s="27">
         <f>'Rozpis podle pokojů'!B24</f>
@@ -4053,10 +3983,9 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Týden 19</t>
-        </is>
+      <c r="A24" s="11">
+        <f>'Rozpis podle pokojů'!A25</f>
+        <v/>
       </c>
       <c r="B24" s="22">
         <f>'Rozpis podle pokojů'!B25</f>
@@ -4108,10 +4037,9 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Týden 20</t>
-        </is>
+      <c r="A25" s="14">
+        <f>'Rozpis podle pokojů'!A26</f>
+        <v/>
       </c>
       <c r="B25" s="27">
         <f>'Rozpis podle pokojů'!B26</f>
@@ -4163,10 +4091,9 @@
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Týden 21</t>
-        </is>
+      <c r="A26" s="11">
+        <f>'Rozpis podle pokojů'!A27</f>
+        <v/>
       </c>
       <c r="B26" s="22">
         <f>'Rozpis podle pokojů'!B27</f>
@@ -4218,10 +4145,9 @@
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>Týden 22</t>
-        </is>
+      <c r="A27" s="14">
+        <f>'Rozpis podle pokojů'!A28</f>
+        <v/>
       </c>
       <c r="B27" s="27">
         <f>'Rozpis podle pokojů'!B28</f>
@@ -4273,10 +4199,9 @@
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Týden 23</t>
-        </is>
+      <c r="A28" s="11">
+        <f>'Rozpis podle pokojů'!A29</f>
+        <v/>
       </c>
       <c r="B28" s="22">
         <f>'Rozpis podle pokojů'!B29</f>
@@ -4328,10 +4253,9 @@
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Týden 24</t>
-        </is>
+      <c r="A29" s="14">
+        <f>'Rozpis podle pokojů'!A30</f>
+        <v/>
       </c>
       <c r="B29" s="27">
         <f>'Rozpis podle pokojů'!B30</f>
@@ -4383,10 +4307,9 @@
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Týden 25</t>
-        </is>
+      <c r="A30" s="11">
+        <f>'Rozpis podle pokojů'!A31</f>
+        <v/>
       </c>
       <c r="B30" s="22">
         <f>'Rozpis podle pokojů'!B31</f>
@@ -4438,10 +4361,9 @@
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Týden 26</t>
-        </is>
+      <c r="A31" s="14">
+        <f>'Rozpis podle pokojů'!A32</f>
+        <v/>
       </c>
       <c r="B31" s="27">
         <f>'Rozpis podle pokojů'!B32</f>
@@ -4493,10 +4415,9 @@
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Týden 27</t>
-        </is>
+      <c r="A32" s="11">
+        <f>'Rozpis podle pokojů'!A33</f>
+        <v/>
       </c>
       <c r="B32" s="22">
         <f>'Rozpis podle pokojů'!B33</f>
@@ -4548,10 +4469,9 @@
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Týden 28</t>
-        </is>
+      <c r="A33" s="14">
+        <f>'Rozpis podle pokojů'!A34</f>
+        <v/>
       </c>
       <c r="B33" s="27">
         <f>'Rozpis podle pokojů'!B34</f>
@@ -4603,10 +4523,9 @@
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Týden 29</t>
-        </is>
+      <c r="A34" s="11">
+        <f>'Rozpis podle pokojů'!A35</f>
+        <v/>
       </c>
       <c r="B34" s="22">
         <f>'Rozpis podle pokojů'!B35</f>
@@ -4658,10 +4577,9 @@
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Týden 30</t>
-        </is>
+      <c r="A35" s="14">
+        <f>'Rozpis podle pokojů'!A36</f>
+        <v/>
       </c>
       <c r="B35" s="27">
         <f>'Rozpis podle pokojů'!B36</f>
@@ -4713,10 +4631,9 @@
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>Týden 31</t>
-        </is>
+      <c r="A36" s="11">
+        <f>'Rozpis podle pokojů'!A37</f>
+        <v/>
       </c>
       <c r="B36" s="22">
         <f>'Rozpis podle pokojů'!B37</f>
@@ -4768,10 +4685,9 @@
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Týden 32</t>
-        </is>
+      <c r="A37" s="14">
+        <f>'Rozpis podle pokojů'!A38</f>
+        <v/>
       </c>
       <c r="B37" s="27">
         <f>'Rozpis podle pokojů'!B38</f>
@@ -4823,10 +4739,9 @@
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Týden 33</t>
-        </is>
+      <c r="A38" s="11">
+        <f>'Rozpis podle pokojů'!A39</f>
+        <v/>
       </c>
       <c r="B38" s="22">
         <f>'Rozpis podle pokojů'!B39</f>
@@ -4878,10 +4793,9 @@
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>Týden 34</t>
-        </is>
+      <c r="A39" s="14">
+        <f>'Rozpis podle pokojů'!A40</f>
+        <v/>
       </c>
       <c r="B39" s="27">
         <f>'Rozpis podle pokojů'!B40</f>
@@ -4933,10 +4847,9 @@
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Týden 35</t>
-        </is>
+      <c r="A40" s="11">
+        <f>'Rozpis podle pokojů'!A41</f>
+        <v/>
       </c>
       <c r="B40" s="22">
         <f>'Rozpis podle pokojů'!B41</f>
@@ -4988,10 +4901,9 @@
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>Týden 36</t>
-        </is>
+      <c r="A41" s="14">
+        <f>'Rozpis podle pokojů'!A42</f>
+        <v/>
       </c>
       <c r="B41" s="27">
         <f>'Rozpis podle pokojů'!B42</f>
@@ -5043,10 +4955,9 @@
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Týden 37</t>
-        </is>
+      <c r="A42" s="11">
+        <f>'Rozpis podle pokojů'!A43</f>
+        <v/>
       </c>
       <c r="B42" s="22">
         <f>'Rozpis podle pokojů'!B43</f>
@@ -5098,10 +5009,9 @@
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>Týden 38</t>
-        </is>
+      <c r="A43" s="14">
+        <f>'Rozpis podle pokojů'!A44</f>
+        <v/>
       </c>
       <c r="B43" s="27">
         <f>'Rozpis podle pokojů'!B44</f>
@@ -5153,10 +5063,9 @@
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>Týden 39</t>
-        </is>
+      <c r="A44" s="11">
+        <f>'Rozpis podle pokojů'!A45</f>
+        <v/>
       </c>
       <c r="B44" s="22">
         <f>'Rozpis podle pokojů'!B45</f>
@@ -5208,10 +5117,9 @@
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>Týden 40</t>
-        </is>
+      <c r="A45" s="14">
+        <f>'Rozpis podle pokojů'!A46</f>
+        <v/>
       </c>
       <c r="B45" s="27">
         <f>'Rozpis podle pokojů'!B46</f>
@@ -5263,10 +5171,9 @@
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>Týden 41</t>
-        </is>
+      <c r="A46" s="11">
+        <f>'Rozpis podle pokojů'!A47</f>
+        <v/>
       </c>
       <c r="B46" s="22">
         <f>'Rozpis podle pokojů'!B47</f>
@@ -5318,10 +5225,9 @@
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>Týden 42</t>
-        </is>
+      <c r="A47" s="14">
+        <f>'Rozpis podle pokojů'!A48</f>
+        <v/>
       </c>
       <c r="B47" s="27">
         <f>'Rozpis podle pokojů'!B48</f>
@@ -5373,10 +5279,9 @@
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>Týden 43</t>
-        </is>
+      <c r="A48" s="11">
+        <f>'Rozpis podle pokojů'!A49</f>
+        <v/>
       </c>
       <c r="B48" s="22">
         <f>'Rozpis podle pokojů'!B49</f>
@@ -5428,10 +5333,9 @@
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>Týden 44</t>
-        </is>
+      <c r="A49" s="14">
+        <f>'Rozpis podle pokojů'!A50</f>
+        <v/>
       </c>
       <c r="B49" s="27">
         <f>'Rozpis podle pokojů'!B50</f>
@@ -5483,10 +5387,9 @@
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Týden 45</t>
-        </is>
+      <c r="A50" s="11">
+        <f>'Rozpis podle pokojů'!A51</f>
+        <v/>
       </c>
       <c r="B50" s="22">
         <f>'Rozpis podle pokojů'!B51</f>
@@ -5538,10 +5441,9 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>Týden 46</t>
-        </is>
+      <c r="A51" s="14">
+        <f>'Rozpis podle pokojů'!A52</f>
+        <v/>
       </c>
       <c r="B51" s="27">
         <f>'Rozpis podle pokojů'!B52</f>
@@ -5593,10 +5495,9 @@
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>Týden 47</t>
-        </is>
+      <c r="A52" s="11">
+        <f>'Rozpis podle pokojů'!A53</f>
+        <v/>
       </c>
       <c r="B52" s="22">
         <f>'Rozpis podle pokojů'!B53</f>
@@ -5648,10 +5549,9 @@
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>Týden 48</t>
-        </is>
+      <c r="A53" s="14">
+        <f>'Rozpis podle pokojů'!A54</f>
+        <v/>
       </c>
       <c r="B53" s="27">
         <f>'Rozpis podle pokojů'!B54</f>
@@ -5703,10 +5603,9 @@
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>Týden 49</t>
-        </is>
+      <c r="A54" s="11">
+        <f>'Rozpis podle pokojů'!A55</f>
+        <v/>
       </c>
       <c r="B54" s="22">
         <f>'Rozpis podle pokojů'!B55</f>
@@ -5758,10 +5657,9 @@
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>Týden 50</t>
-        </is>
+      <c r="A55" s="14">
+        <f>'Rozpis podle pokojů'!A56</f>
+        <v/>
       </c>
       <c r="B55" s="27">
         <f>'Rozpis podle pokojů'!B56</f>
@@ -5813,10 +5711,9 @@
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>Týden 51</t>
-        </is>
+      <c r="A56" s="11">
+        <f>'Rozpis podle pokojů'!A57</f>
+        <v/>
       </c>
       <c r="B56" s="22">
         <f>'Rozpis podle pokojů'!B57</f>
@@ -5868,10 +5765,9 @@
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>Týden 52</t>
-        </is>
+      <c r="A57" s="14">
+        <f>'Rozpis podle pokojů'!A58</f>
+        <v/>
       </c>
       <c r="B57" s="27">
         <f>'Rozpis podle pokojů'!B58</f>
@@ -5940,7 +5836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6011,43 +5907,43 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>Zkontrolovat, že na mezipatře / schodech nezůstaly žádné odpadky, letáky nebo kamínky.</t>
+          <t>Zkontrolovat, že na mezipatře / schodech nezůstaly žádné odpadky ani nepořádek.</t>
         </is>
       </c>
       <c r="F7" s="33" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+    <row r="8" ht="6" customHeight="1">
+      <c r="A8" s="34" t="n"/>
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="36" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>🍳  KUCHYŇ   —   (Společná zóna vaření)</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="39" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>Doporučený čas splnění: pátek odpoledne nebo sobota dopoledne.</t>
-        </is>
-      </c>
-      <c r="F8" s="33" t="n"/>
-    </row>
-    <row r="9" ht="6" customHeight="1">
-      <c r="A9" s="34" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="36" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
-        <is>
-          <t>🍳  KUCHYŇ   —   (Společná zóna vaření)</t>
-        </is>
-      </c>
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="38" t="n"/>
-      <c r="F11" s="39" t="n"/>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>Starat se o kuchyňskou linku, dřez a varnou desku (otírat mastnotu a drobky).</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="31" t="inlineStr">
@@ -6057,7 +5953,7 @@
       </c>
       <c r="B12" s="32" t="inlineStr">
         <is>
-          <t>Starat se o kuchyňskou linku, dřez a varnou desku (otírat mastnotu a drobky).</t>
+          <t>Průběžně vyndávat umytou myčku a uklízet nádobí do skříněk.</t>
         </is>
       </c>
       <c r="F12" s="40" t="n"/>
@@ -6070,7 +5966,7 @@
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>Průběžně vyndávat umytou myčku a uklízet nádobí do skříněk.</t>
+          <t>Zapnout myčku, jakmile se naplní (nenechávat špinavé nádobí hromadit ve dřezu).</t>
         </is>
       </c>
       <c r="F13" s="40" t="n"/>
@@ -6083,43 +5979,43 @@
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>Zapnout myčku, jakmile se naplní (nenechávat špinavé nádobí hromadit ve dřezu).</t>
+          <t>Pravidelně zametat a vytírat podlahu v kuchyni (dle potřeby i v týdnu, min. 1× důkladně na závěr).</t>
         </is>
       </c>
       <c r="F14" s="40" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+    <row r="15" ht="6" customHeight="1">
+      <c r="A15" s="41" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="43" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>🗑️  ODPADKY   —   (Čistý a voňavý byt)</t>
+        </is>
+      </c>
+      <c r="B17" s="45" t="n"/>
+      <c r="C17" s="45" t="n"/>
+      <c r="D17" s="45" t="n"/>
+      <c r="E17" s="45" t="n"/>
+      <c r="F17" s="46" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Pravidelně zametat a vytírat podlahu v kuchyni (dle potřeby i v týdnu, min. 1× důkladně na závěr).</t>
-        </is>
-      </c>
-      <c r="F15" s="40" t="n"/>
-    </row>
-    <row r="16" ht="6" customHeight="1">
-      <c r="A16" s="41" t="n"/>
-      <c r="B16" s="42" t="n"/>
-      <c r="C16" s="42" t="n"/>
-      <c r="D16" s="42" t="n"/>
-      <c r="E16" s="42" t="n"/>
-      <c r="F16" s="43" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
-        <is>
-          <t>🗑️  ODPADKY   —   (Čistý a voňavý byt)</t>
-        </is>
-      </c>
-      <c r="B18" s="45" t="n"/>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="46" t="n"/>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Pravidelně vynášet pytle se směsným odpadem, jakmile jsou plné (nečekat na přetečení).</t>
+        </is>
+      </c>
+      <c r="F18" s="47" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
@@ -6129,7 +6025,7 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>Pravidelně vynášet pytle se směsným odpadem, jakmile jsou plné (nečekat na přetečení).</t>
+          <t>Po vynesení koše VŽDY ihned nasadit nový čistý pytel!</t>
         </is>
       </c>
       <c r="F19" s="47" t="n"/>
@@ -6142,7 +6038,7 @@
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>Po vynesení koše VŽDY ihned nasadit nový čistý pytel!</t>
+          <t>Vynášet tříděný odpad (plast, papír, plechovky, sklo) do příslušných kontejnerů.</t>
         </is>
       </c>
       <c r="F20" s="47" t="n"/>
@@ -6155,7 +6051,7 @@
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>Vynášet tříděný odpad (plast, papír, plechovky, sklo) do příslušných kontejnerů.</t>
+          <t>Umýt odpadkový koš, pokud prosákl pytel nebo někdo něco hodil vedle.</t>
         </is>
       </c>
       <c r="F21" s="47" t="n"/>
@@ -6286,7 +6182,7 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Důkladně vymýt sprchový kout / vanu a odstranit vlasy ze sítka/odpadu.</t>
+          <t>Důkladně vymýt sprchový kout a vyčistit sítko od vlasů.</t>
         </is>
       </c>
       <c r="F34" s="33" t="n"/>
@@ -6412,12 +6308,12 @@
       </c>
       <c r="B47" s="68" t="inlineStr">
         <is>
-          <t>Předání služeb:</t>
+          <t>Průběžný pořádek:</t>
         </is>
       </c>
       <c r="C47" s="69" t="inlineStr">
         <is>
-          <t>Služba se oficiálně předává v NEDĚLI do 20:00 (do té doby je vše hotovo).</t>
+          <t>Služba neslouží jako osobní uklízeč! Každý po sobě ihned utře linku, když něco rozlije nebo rozsype, a udržuje společné prostory v čistotě.</t>
         </is>
       </c>
       <c r="D47" s="70" t="n"/>
@@ -6432,12 +6328,12 @@
       </c>
       <c r="B48" s="68" t="inlineStr">
         <is>
-          <t>Nepřítomnost:</t>
+          <t>Žádné nádobí ve dřezu:</t>
         </is>
       </c>
       <c r="C48" s="69" t="inlineStr">
         <is>
-          <t>Když někdo odjíždí na týden pryč, je jeho povinností si zajistit výměnu s jiným pokojem.</t>
+          <t>Ve dřezu nesmí zůstávat žádné nádobí – plný dřez se pak nedá vůbec používat. Při plné myčce odložit vedle na linku a po vyklizení dát do myčky, nebo hned umýt.</t>
         </is>
       </c>
       <c r="D48" s="70" t="n"/>
@@ -6452,12 +6348,12 @@
       </c>
       <c r="B49" s="68" t="inlineStr">
         <is>
-          <t>Průběžný pořádek:</t>
+          <t>Nepřítomnost a odjezdy:</t>
         </is>
       </c>
       <c r="C49" s="69" t="inlineStr">
         <is>
-          <t>Služba neuklízí cizí nepořádek! Každý po sobě ihned utře linku, když něco rozlije, a udržuje pořádek.</t>
+          <t>Když někdo odjíždí na týden pryč, je jeho povinností si zajistit výměnu s jiným pokojem.</t>
         </is>
       </c>
       <c r="D49" s="70" t="n"/>
@@ -6472,57 +6368,39 @@
       </c>
       <c r="B50" s="68" t="inlineStr">
         <is>
-          <t>Žádné nádobí ve dřezu:</t>
+          <t>Spotřební materiál a chemie:</t>
         </is>
       </c>
       <c r="C50" s="69" t="inlineStr">
         <is>
-          <t>Ve dřezu nesmí zůstávat nádobí – plný dřez se nedá používat. Při plné myčce odložit vedle na linku a pak do myčky, nebo hned umýt.</t>
+          <t>Když dochází jar, tablety do myčky, WC gel, toaletní papír nebo pytle do koše, tak to koupíš a hodíš do SettleUp.</t>
         </is>
       </c>
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="67" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="B51" s="68" t="inlineStr">
-        <is>
-          <t>Spotřební materiál a chemie:</t>
-        </is>
-      </c>
-      <c r="C51" s="69" t="inlineStr">
-        <is>
-          <t>Když dochází jar, tablety do myčky, WC gel, toaletní papír nebo pytle do koše, tak to koupíš a hodíš do SettleUp.</t>
-        </is>
-      </c>
-      <c r="D51" s="70" t="n"/>
-      <c r="E51" s="70" t="n"/>
-      <c r="F51" s="70" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="37">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="C49:F49"/>
+    <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B8:F8"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A10:F10"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B28:F28"/>
@@ -6531,15 +6409,12 @@
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="C50:F50"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="C51:F51"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="A25:F25"/>
